--- a/Docs/tablas/Resumen_Climatico_Completo.xlsx
+++ b/Docs/tablas/Resumen_Climatico_Completo.xlsx
@@ -16,12 +16,14 @@
     <sheet name="T8_Climatol_Mensual" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="T9_Heatmap_Datos" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="T10_Heliofania_ETP" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="T10b_Helio_ETP_Desc" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="T11_MannKendall" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="142">
   <si>
     <t xml:space="preserve">Estadísticos descriptivos generales por variable (1968-2024)</t>
   </si>
@@ -342,6 +344,111 @@
   </si>
   <si>
     <t xml:space="preserve">Excluido — registros incompletos período COVID-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estadísticos descriptivos de heliofanía y ETP — base de Tabla 4 del manuscrito</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliofania_Total_hs_Media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliofania_Total_hs_DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliofania_Total_hs_Minimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliofania_Total_hs_P25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliofania_Total_hs_Mediana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliofania_Total_hs_P75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heliofania_Total_hs_Maximo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETP_Total_mm_Media</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETP_Total_mm_DE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETP_Total_mm_Minimo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETP_Total_mm_P25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETP_Total_mm_Mediana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETP_Total_mm_P75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ETP_Total_mm_Maximo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mann-Kendall + pendiente de Sen — variables anuales principales | ~ p&lt;=0.10 | * p&lt;0.05 | ** p&lt;0.01 | *** p&lt;0.001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pendiente_Sen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tau</t>
+  </si>
+  <si>
+    <t xml:space="preserve">p_valor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temp. media anual (°C/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temp. máx. media (°C/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Temp. mín. media (°C/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precipitación total (mm/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días con lluvia (días/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intensidad media (mm/d/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días P95 (días/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días P99 (días/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precip. máx. diaria (mm/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Racha seca máx. CDD (días/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">**</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días calor extremo &gt;=35°C (días/año)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Días helada (días/año)</t>
   </si>
 </sst>
 </file>
@@ -1958,6 +2065,370 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="71.025" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="22.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="26.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="23.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="27.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="23.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="26.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="18.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="15.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="19.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="16.71" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="20.71" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="16.71" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="19.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="n">
+        <v>2612</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>124.3</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>2386.7</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2492.1</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>2599.4</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>2700.6</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>2869.3</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>1310.4</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>119.3</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>1037.7</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>1246.6</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>1308.3</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>1381.1</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>1542.6</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <cols>
+    <col min="1" max="1" width="108.755" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="13.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="6.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="3.71" hidden="0" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>0.0918</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>0.0053</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>0.069</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.4647</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>0.2385</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>3.8727</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>0.2385</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>-0.008</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>0.9405</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>0.0398</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>0.0323</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>0.0774</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>0.0385</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>0.5792</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>0.1172</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B13" s="4" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.0034</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>0.1364</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="4" t="n">
+        <v>0.0217</v>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>0.1942</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <dimension ref="A1"/>
